--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DFS_HRM-2031-0452/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DFS_HRM-2031-0452/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.72028</v>
+        <v>17.20389</v>
       </c>
       <c r="D2" t="n">
-        <v>16.64102</v>
+        <v>16.65586</v>
       </c>
       <c r="E2" t="n">
-        <v>16.6078</v>
+        <v>16.86049</v>
       </c>
       <c r="F2" t="n">
-        <v>43.63326</v>
+        <v>42.2262</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05066</v>
+        <v>0.05101</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80962</v>
+        <v>1.83647</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.72237</v>
+        <v>16.98731</v>
       </c>
       <c r="D3" t="n">
-        <v>16.47961</v>
+        <v>16.50772</v>
       </c>
       <c r="E3" t="n">
-        <v>16.71189</v>
+        <v>16.91493</v>
       </c>
       <c r="F3" t="n">
-        <v>42.29993</v>
+        <v>42.06314</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05042</v>
+        <v>0.04972</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85751</v>
+        <v>1.83073</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.81331</v>
+        <v>16.97686</v>
       </c>
       <c r="D4" t="n">
-        <v>16.59394</v>
+        <v>16.87342</v>
       </c>
       <c r="E4" t="n">
-        <v>16.90321</v>
+        <v>16.89339</v>
       </c>
       <c r="F4" t="n">
-        <v>42.45939</v>
+        <v>42.51966</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0499</v>
+        <v>0.04929</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82992</v>
+        <v>1.82404</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.51039</v>
+        <v>16.53908</v>
       </c>
       <c r="D6" t="n">
-        <v>16.14741</v>
+        <v>16.19769</v>
       </c>
       <c r="E6" t="n">
-        <v>16.07345</v>
+        <v>16.29039</v>
       </c>
       <c r="F6" t="n">
-        <v>21.74866</v>
+        <v>22.04124</v>
       </c>
       <c r="G6" t="n">
-        <v>34.12696</v>
+        <v>34.60848</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.63396</v>
+        <v>16.4735</v>
       </c>
       <c r="D7" t="n">
-        <v>15.97059</v>
+        <v>16.14708</v>
       </c>
       <c r="E7" t="n">
-        <v>16.73921</v>
+        <v>16.30326</v>
       </c>
       <c r="F7" t="n">
-        <v>21.59861</v>
+        <v>21.93301</v>
       </c>
       <c r="G7" t="n">
-        <v>33.58477</v>
+        <v>34.17269</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.80289</v>
+        <v>16.89541</v>
       </c>
       <c r="D8" t="n">
-        <v>16.04169</v>
+        <v>16.34162</v>
       </c>
       <c r="E8" t="n">
-        <v>16.53397</v>
+        <v>16.38731</v>
       </c>
       <c r="F8" t="n">
-        <v>21.89581</v>
+        <v>21.84194</v>
       </c>
       <c r="G8" t="n">
-        <v>34.21346</v>
+        <v>33.99258</v>
       </c>
     </row>
   </sheetData>
